--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:31</t>
+    <t xml:space="preserve">2026-09-24 01:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>-0.42</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -587,7 +587,7 @@
         <v>-0.59</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -606,7 +606,7 @@
         <v>-0.34</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -625,7 +625,7 @@
         <v>0.34</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -644,7 +644,7 @@
         <v>0.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -665,7 +665,7 @@
         <v>0.2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.06</v>
@@ -688,10 +688,10 @@
         <v>-0.03</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>-0.48</v>
@@ -732,7 +732,7 @@
         <v>0.21</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -751,7 +751,7 @@
         <v>0.21</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -772,7 +772,7 @@
         <v>0.38</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.34</v>
@@ -795,7 +795,7 @@
         <v>0.31</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.42</v>
@@ -815,13 +815,13 @@
         <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="15">
@@ -838,13 +838,13 @@
         <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="16">
@@ -861,13 +861,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="17">
@@ -884,13 +884,13 @@
         <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="18">
@@ -908,7 +908,7 @@
         <v>-0.75</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2"/>
     </row>
@@ -929,7 +929,7 @@
         <v>-0.46</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.35</v>
@@ -952,7 +952,7 @@
         <v>-0.42</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.2</v>
@@ -972,13 +972,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="22">
@@ -995,13 +995,13 @@
         <v>7</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.29</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_tarapaca.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:21</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
